--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/140.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/140.xlsx
@@ -426,13 +426,13 @@
         <v>-16.77694870400907</v>
       </c>
       <c r="E2">
-        <v>-15.88335747864493</v>
+        <v>-12.42295123652767</v>
       </c>
       <c r="F2">
-        <v>2.088455726035924</v>
+        <v>3.41826042550686</v>
       </c>
       <c r="G2">
-        <v>-8.868684496187162</v>
+        <v>-5.447997106824424</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.91233241038237</v>
       </c>
       <c r="E3">
-        <v>-16.46473202869766</v>
+        <v>-12.50888355929722</v>
       </c>
       <c r="F3">
-        <v>2.154733401933913</v>
+        <v>3.443664797015916</v>
       </c>
       <c r="G3">
-        <v>-7.886054990311768</v>
+        <v>-4.882655245083083</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.94171725646004</v>
       </c>
       <c r="E4">
-        <v>-16.76458040664155</v>
+        <v>-13.95155575171283</v>
       </c>
       <c r="F4">
-        <v>2.31245786889655</v>
+        <v>3.594346484319952</v>
       </c>
       <c r="G4">
-        <v>-7.620029482412553</v>
+        <v>-4.773595943382873</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.83524875422005</v>
       </c>
       <c r="E5">
-        <v>-18.17584310333995</v>
+        <v>-15.0579796921109</v>
       </c>
       <c r="F5">
-        <v>2.492218565508459</v>
+        <v>3.44122774011688</v>
       </c>
       <c r="G5">
-        <v>-7.279788164613957</v>
+        <v>-3.891054160796263</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.59138454241025</v>
       </c>
       <c r="E6">
-        <v>-18.60955770142458</v>
+        <v>-17.03088637761062</v>
       </c>
       <c r="F6">
-        <v>2.21535001500117</v>
+        <v>3.791282550661506</v>
       </c>
       <c r="G6">
-        <v>-6.755093181003788</v>
+        <v>-3.904322827317662</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.21315356155456</v>
       </c>
       <c r="E7">
-        <v>-19.40404676675229</v>
+        <v>-16.6905760844082</v>
       </c>
       <c r="F7">
-        <v>2.340509702624952</v>
+        <v>4.086395064848052</v>
       </c>
       <c r="G7">
-        <v>-6.901584821116538</v>
+        <v>-3.016285539135862</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.70658922837117</v>
       </c>
       <c r="E8">
-        <v>-19.39451432896615</v>
+        <v>-18.53210268199739</v>
       </c>
       <c r="F8">
-        <v>2.8091370232063</v>
+        <v>3.794831276615099</v>
       </c>
       <c r="G8">
-        <v>-6.196607459074277</v>
+        <v>-2.753650029868861</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.07061334812146</v>
       </c>
       <c r="E9">
-        <v>-20.71779330416953</v>
+        <v>-18.16549101175842</v>
       </c>
       <c r="F9">
-        <v>2.515073222151698</v>
+        <v>3.647970019772774</v>
       </c>
       <c r="G9">
-        <v>-5.238055550906002</v>
+        <v>-1.894394624605485</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.31670711645234</v>
       </c>
       <c r="E10">
-        <v>-22.40245809060702</v>
+        <v>-20.00703572324364</v>
       </c>
       <c r="F10">
-        <v>2.278685329884414</v>
+        <v>4.143827433618948</v>
       </c>
       <c r="G10">
-        <v>-4.908398047196456</v>
+        <v>-1.258458689784726</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.43972958888308</v>
       </c>
       <c r="E11">
-        <v>-23.21548220004813</v>
+        <v>-20.4900065331097</v>
       </c>
       <c r="F11">
-        <v>2.533058735201281</v>
+        <v>3.601735521552923</v>
       </c>
       <c r="G11">
-        <v>-4.20185810765966</v>
+        <v>-0.7548320179864787</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.46296152770875</v>
       </c>
       <c r="E12">
-        <v>-23.33487088878635</v>
+        <v>-20.93471626608495</v>
       </c>
       <c r="F12">
-        <v>2.756736158040009</v>
+        <v>3.886601130966839</v>
       </c>
       <c r="G12">
-        <v>-3.8296534726794</v>
+        <v>0.7434050239937861</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.39133882782609</v>
       </c>
       <c r="E13">
-        <v>-24.2119185637479</v>
+        <v>-22.25204029796824</v>
       </c>
       <c r="F13">
-        <v>2.951322974427224</v>
+        <v>3.960882492710676</v>
       </c>
       <c r="G13">
-        <v>-2.685280643391833</v>
+        <v>0.7087833387440879</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.26469297880181</v>
       </c>
       <c r="E14">
-        <v>-24.45696787772496</v>
+        <v>-24.10335292788801</v>
       </c>
       <c r="F14">
-        <v>3.157936028768282</v>
+        <v>4.354096901675963</v>
       </c>
       <c r="G14">
-        <v>-2.28806152631684</v>
+        <v>1.700453944487233</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.104360686316992</v>
       </c>
       <c r="E15">
-        <v>-26.55779036851935</v>
+        <v>-24.52658410864488</v>
       </c>
       <c r="F15">
-        <v>3.238894031778683</v>
+        <v>4.185206042123588</v>
       </c>
       <c r="G15">
-        <v>-1.703687338270229</v>
+        <v>2.674638248691947</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.949835776155436</v>
       </c>
       <c r="E16">
-        <v>-27.63998244450237</v>
+        <v>-25.3883255414605</v>
       </c>
       <c r="F16">
-        <v>3.191736732272113</v>
+        <v>4.526080885110391</v>
       </c>
       <c r="G16">
-        <v>-0.7744602424888176</v>
+        <v>3.359835101137062</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.829179389646869</v>
       </c>
       <c r="E17">
-        <v>-27.876509170397</v>
+        <v>-26.36201990869375</v>
       </c>
       <c r="F17">
-        <v>3.55368358525133</v>
+        <v>5.009101917682782</v>
       </c>
       <c r="G17">
-        <v>-0.2150111518073797</v>
+        <v>3.727001085806551</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.773585167949927</v>
       </c>
       <c r="E18">
-        <v>-29.06195045375491</v>
+        <v>-27.49598149953246</v>
       </c>
       <c r="F18">
-        <v>3.163345267908563</v>
+        <v>5.000551509351085</v>
       </c>
       <c r="G18">
-        <v>-0.2774778355878877</v>
+        <v>3.471728229818889</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.813220767439502</v>
       </c>
       <c r="E19">
-        <v>-29.02452714455552</v>
+        <v>-28.09332344893625</v>
       </c>
       <c r="F19">
-        <v>3.912913393149363</v>
+        <v>5.095611639026746</v>
       </c>
       <c r="G19">
-        <v>0.09233327496747877</v>
+        <v>5.066411394994741</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.969528405245696</v>
       </c>
       <c r="E20">
-        <v>-30.05335568283216</v>
+        <v>-28.48670292903455</v>
       </c>
       <c r="F20">
-        <v>4.004984773235722</v>
+        <v>5.439539844260267</v>
       </c>
       <c r="G20">
-        <v>0.6999309399720768</v>
+        <v>5.638361105632467</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.268986058524851</v>
       </c>
       <c r="E21">
-        <v>-30.74689600558088</v>
+        <v>-28.57071517882486</v>
       </c>
       <c r="F21">
-        <v>4.123681538382864</v>
+        <v>5.760020281790145</v>
       </c>
       <c r="G21">
-        <v>1.076717369978688</v>
+        <v>5.357769197360459</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.717524761663003</v>
       </c>
       <c r="E22">
-        <v>-31.25078836536238</v>
+        <v>-28.99075831388032</v>
       </c>
       <c r="F22">
-        <v>3.851859402093428</v>
+        <v>5.850668526678495</v>
       </c>
       <c r="G22">
-        <v>1.066865186453817</v>
+        <v>5.475657724013906</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.328593003589695</v>
       </c>
       <c r="E23">
-        <v>-30.77905043527235</v>
+        <v>-28.23417710447082</v>
       </c>
       <c r="F23">
-        <v>4.540794346918916</v>
+        <v>5.626146169088912</v>
       </c>
       <c r="G23">
-        <v>1.844724208543132</v>
+        <v>5.99655882243607</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.087244138961305</v>
       </c>
       <c r="E24">
-        <v>-31.43054161262285</v>
+        <v>-29.24379132753291</v>
       </c>
       <c r="F24">
-        <v>4.099474986138256</v>
+        <v>5.508229726035208</v>
       </c>
       <c r="G24">
-        <v>1.077038492895997</v>
+        <v>7.029488757235152</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.988576247197998</v>
       </c>
       <c r="E25">
-        <v>-31.53606411394958</v>
+        <v>-29.33083312643435</v>
       </c>
       <c r="F25">
-        <v>4.586622945111396</v>
+        <v>5.528493249442489</v>
       </c>
       <c r="G25">
-        <v>2.207540136374018</v>
+        <v>5.702807495645459</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.003762270760551</v>
       </c>
       <c r="E26">
-        <v>-32.09142258082825</v>
+        <v>-29.21117272925567</v>
       </c>
       <c r="F26">
-        <v>4.438416419606924</v>
+        <v>5.314126676211227</v>
       </c>
       <c r="G26">
-        <v>1.706124908996004</v>
+        <v>5.96648913730287</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.113471659799415</v>
       </c>
       <c r="E27">
-        <v>-30.90792854129364</v>
+        <v>-29.21168897529254</v>
       </c>
       <c r="F27">
-        <v>4.196877738829033</v>
+        <v>5.376610429404394</v>
       </c>
       <c r="G27">
-        <v>1.697567148776988</v>
+        <v>5.411870132563228</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.286277834199291</v>
       </c>
       <c r="E28">
-        <v>-31.21923848695094</v>
+        <v>-30.01879210496861</v>
       </c>
       <c r="F28">
-        <v>4.034506130736691</v>
+        <v>5.607044016780355</v>
       </c>
       <c r="G28">
-        <v>0.9780366285440921</v>
+        <v>5.68276876349625</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.499860235433518</v>
       </c>
       <c r="E29">
-        <v>-31.74244478837515</v>
+        <v>-29.57061129666648</v>
       </c>
       <c r="F29">
-        <v>4.214096183663624</v>
+        <v>5.39265590599662</v>
       </c>
       <c r="G29">
-        <v>0.2695633304123617</v>
+        <v>4.359278867806416</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.731364599163454</v>
       </c>
       <c r="E30">
-        <v>-30.53772126269258</v>
+        <v>-29.00071189974918</v>
       </c>
       <c r="F30">
-        <v>3.735624544867407</v>
+        <v>5.357067585637548</v>
       </c>
       <c r="G30">
-        <v>0.4354481462941624</v>
+        <v>5.120588472744914</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.965882407046972</v>
       </c>
       <c r="E31">
-        <v>-30.86565523643204</v>
+        <v>-28.61224128547519</v>
       </c>
       <c r="F31">
-        <v>4.143333726646879</v>
+        <v>5.738220965218074</v>
       </c>
       <c r="G31">
-        <v>-0.01147881205298712</v>
+        <v>4.062793030400367</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.19268409486182</v>
       </c>
       <c r="E32">
-        <v>-31.32528176278856</v>
+        <v>-28.44827882707947</v>
       </c>
       <c r="F32">
-        <v>4.35847233829755</v>
+        <v>5.307895696607369</v>
       </c>
       <c r="G32">
-        <v>0.2098543310660666</v>
+        <v>4.150863473381598</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.404366219845271</v>
       </c>
       <c r="E33">
-        <v>-29.94782638879441</v>
+        <v>-27.93129012046779</v>
       </c>
       <c r="F33">
-        <v>4.140063332140627</v>
+        <v>5.383220801278735</v>
       </c>
       <c r="G33">
-        <v>-0.538259439352897</v>
+        <v>3.87617426780611</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.59922551281072</v>
       </c>
       <c r="E34">
-        <v>-30.27846612575345</v>
+        <v>-28.1011531804955</v>
       </c>
       <c r="F34">
-        <v>4.629804081084528</v>
+        <v>5.251407666675665</v>
       </c>
       <c r="G34">
-        <v>-0.1277153764823378</v>
+        <v>3.964678392252986</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.77380510990749</v>
       </c>
       <c r="E35">
-        <v>-29.92076196388757</v>
+        <v>-26.70135205151051</v>
       </c>
       <c r="F35">
-        <v>4.575348864759294</v>
+        <v>5.58923246088536</v>
       </c>
       <c r="G35">
-        <v>-1.148085101505425</v>
+        <v>3.240870647183352</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.931758897738423</v>
       </c>
       <c r="E36">
-        <v>-28.64235110915219</v>
+        <v>-26.83342499594422</v>
       </c>
       <c r="F36">
-        <v>4.169964081912077</v>
+        <v>5.880935414841984</v>
       </c>
       <c r="G36">
-        <v>-2.117618089227463</v>
+        <v>2.907127930278345</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.071447632022522</v>
       </c>
       <c r="E37">
-        <v>-28.65195147404845</v>
+        <v>-26.59774056621502</v>
       </c>
       <c r="F37">
-        <v>4.529160755113999</v>
+        <v>5.75002023050355</v>
       </c>
       <c r="G37">
-        <v>-1.478090212496594</v>
+        <v>3.019411703333806</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.200221876053738</v>
       </c>
       <c r="E38">
-        <v>-27.65628042245598</v>
+        <v>-25.02062703745969</v>
       </c>
       <c r="F38">
-        <v>4.493287476368364</v>
+        <v>6.363707937193536</v>
       </c>
       <c r="G38">
-        <v>-1.693338572914468</v>
+        <v>2.164023015260299</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.317445267324829</v>
       </c>
       <c r="E39">
-        <v>-27.19568933113583</v>
+        <v>-24.3620555909982</v>
       </c>
       <c r="F39">
-        <v>4.991383138936901</v>
+        <v>6.110078405804383</v>
       </c>
       <c r="G39">
-        <v>-1.705855745598452</v>
+        <v>2.568088340510504</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.430556244728889</v>
       </c>
       <c r="E40">
-        <v>-26.92689269946254</v>
+        <v>-24.23840107974475</v>
       </c>
       <c r="F40">
-        <v>4.766579136430366</v>
+        <v>6.257715014535727</v>
       </c>
       <c r="G40">
-        <v>-2.656485518291252</v>
+        <v>1.349843998059639</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.539688982345325</v>
       </c>
       <c r="E41">
-        <v>-26.19615549121481</v>
+        <v>-24.31103327435378</v>
       </c>
       <c r="F41">
-        <v>5.134099245295617</v>
+        <v>6.215400350865923</v>
       </c>
       <c r="G41">
-        <v>-2.895007013850202</v>
+        <v>2.414359847848907</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.648620346169212</v>
       </c>
       <c r="E42">
-        <v>-25.8677188568605</v>
+        <v>-23.42998242836945</v>
       </c>
       <c r="F42">
-        <v>4.958018156686943</v>
+        <v>6.086836073216634</v>
       </c>
       <c r="G42">
-        <v>-1.97568175977675</v>
+        <v>2.346626086115419</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.757904194869617</v>
       </c>
       <c r="E43">
-        <v>-24.72057940665947</v>
+        <v>-23.20118580760591</v>
       </c>
       <c r="F43">
-        <v>5.301076576147524</v>
+        <v>6.37915533252094</v>
       </c>
       <c r="G43">
-        <v>-2.90986805277599</v>
+        <v>2.045128082762913</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.867589276340657</v>
       </c>
       <c r="E44">
-        <v>-24.86544076169084</v>
+        <v>-22.43922024260129</v>
       </c>
       <c r="F44">
-        <v>5.10134725492373</v>
+        <v>6.290809949012373</v>
       </c>
       <c r="G44">
-        <v>-3.067297735350492</v>
+        <v>1.499805089897545</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.980394472854657</v>
       </c>
       <c r="E45">
-        <v>-23.66566685809865</v>
+        <v>-21.18269550274498</v>
       </c>
       <c r="F45">
-        <v>5.227220995248726</v>
+        <v>6.553599567141683</v>
       </c>
       <c r="G45">
-        <v>-2.501628129600764</v>
+        <v>1.303681751060042</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.094022327953233</v>
       </c>
       <c r="E46">
-        <v>-23.24154356796227</v>
+        <v>-20.27895700198222</v>
       </c>
       <c r="F46">
-        <v>5.327191686888181</v>
+        <v>6.469334721459306</v>
       </c>
       <c r="G46">
-        <v>-3.060425042810965</v>
+        <v>1.963913779593512</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.215391125720006</v>
       </c>
       <c r="E47">
-        <v>-23.00877094702</v>
+        <v>-20.00066416031485</v>
       </c>
       <c r="F47">
-        <v>5.452189014501015</v>
+        <v>6.562360380793691</v>
       </c>
       <c r="G47">
-        <v>-2.218798292544208</v>
+        <v>0.9555911297878334</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.341174118118904</v>
       </c>
       <c r="E48">
-        <v>-21.75120012966792</v>
+        <v>-19.45038664127279</v>
       </c>
       <c r="F48">
-        <v>5.298510293933651</v>
+        <v>6.758413407483861</v>
       </c>
       <c r="G48">
-        <v>-3.222588805506625</v>
+        <v>0.7083728310972184</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.480438376708197</v>
       </c>
       <c r="E49">
-        <v>-21.29453522531242</v>
+        <v>-19.06523539844641</v>
       </c>
       <c r="F49">
-        <v>5.648384520384467</v>
+        <v>6.563733813947533</v>
       </c>
       <c r="G49">
-        <v>-3.257157522027695</v>
+        <v>0.4471840302308788</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.629714412615335</v>
       </c>
       <c r="E50">
-        <v>-21.49178196766451</v>
+        <v>-19.05208923840215</v>
       </c>
       <c r="F50">
-        <v>5.692196872318533</v>
+        <v>6.747437539396767</v>
       </c>
       <c r="G50">
-        <v>-2.619255123156608</v>
+        <v>0.5215388830429096</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.797902768859411</v>
       </c>
       <c r="E51">
-        <v>-20.6423851549938</v>
+        <v>-18.25061726615461</v>
       </c>
       <c r="F51">
-        <v>5.562318803968404</v>
+        <v>6.613243676878053</v>
       </c>
       <c r="G51">
-        <v>-3.612521411849682</v>
+        <v>0.02934683553730516</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.983130382840283</v>
       </c>
       <c r="E52">
-        <v>-19.79195132177533</v>
+        <v>-17.44819431436546</v>
       </c>
       <c r="F52">
-        <v>5.465572118260645</v>
+        <v>6.869858644386895</v>
       </c>
       <c r="G52">
-        <v>-3.554583554366896</v>
+        <v>-0.2857608205271442</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.190592085491402</v>
       </c>
       <c r="E53">
-        <v>-19.79680584591155</v>
+        <v>-17.0123377480752</v>
       </c>
       <c r="F53">
-        <v>5.487358180954272</v>
+        <v>7.199800694391549</v>
       </c>
       <c r="G53">
-        <v>-3.549839542609121</v>
+        <v>-0.8707375278619023</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.419895614688403</v>
       </c>
       <c r="E54">
-        <v>-19.26797065129581</v>
+        <v>-16.48910880428095</v>
       </c>
       <c r="F54">
-        <v>5.503461643264694</v>
+        <v>6.432618164697621</v>
       </c>
       <c r="G54">
-        <v>-4.370268869787925</v>
+        <v>-1.10304512944364</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.6703563665457</v>
       </c>
       <c r="E55">
-        <v>-19.49169990964476</v>
+        <v>-16.37817930498906</v>
       </c>
       <c r="F55">
-        <v>5.491443688984878</v>
+        <v>6.668928190429042</v>
       </c>
       <c r="G55">
-        <v>-4.205383838658983</v>
+        <v>-0.9941977026579426</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.942528568032127</v>
       </c>
       <c r="E56">
-        <v>-18.79191934971347</v>
+        <v>-15.24344334509504</v>
       </c>
       <c r="F56">
-        <v>5.309873837965255</v>
+        <v>6.88119899413122</v>
       </c>
       <c r="G56">
-        <v>-4.656055024011049</v>
+        <v>-1.410849722048457</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.228884156993646</v>
       </c>
       <c r="E57">
-        <v>-17.59214544612128</v>
+        <v>-14.5713227044026</v>
       </c>
       <c r="F57">
-        <v>5.454089289323037</v>
+        <v>6.787532178427069</v>
       </c>
       <c r="G57">
-        <v>-4.975813996558174</v>
+        <v>-1.987871188452347</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.531633527542673</v>
       </c>
       <c r="E58">
-        <v>-18.56124341223675</v>
+        <v>-14.07296866833248</v>
       </c>
       <c r="F58">
-        <v>5.700024944274988</v>
+        <v>6.631167890739829</v>
       </c>
       <c r="G58">
-        <v>-5.119256624229256</v>
+        <v>-1.868913355589715</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.838240123651389</v>
       </c>
       <c r="E59">
-        <v>-17.14556998185487</v>
+        <v>-13.29058874250128</v>
       </c>
       <c r="F59">
-        <v>5.332624120315741</v>
+        <v>6.891619856058438</v>
       </c>
       <c r="G59">
-        <v>-5.202410907084669</v>
+        <v>-2.300082117169933</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.151877359332204</v>
       </c>
       <c r="E60">
-        <v>-17.00642356102118</v>
+        <v>-14.30136225490934</v>
       </c>
       <c r="F60">
-        <v>5.615571230824774</v>
+        <v>6.5584869348182</v>
       </c>
       <c r="G60">
-        <v>-5.332651079145137</v>
+        <v>-2.285098588059192</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.457228236522964</v>
       </c>
       <c r="E61">
-        <v>-15.98509417570125</v>
+        <v>-13.45351418034925</v>
       </c>
       <c r="F61">
-        <v>5.445267176483223</v>
+        <v>6.753753012475711</v>
       </c>
       <c r="G61">
-        <v>-5.667486276078104</v>
+        <v>-3.411349491064789</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.754351534195727</v>
       </c>
       <c r="E62">
-        <v>-16.39049222581592</v>
+        <v>-13.57585090566646</v>
       </c>
       <c r="F62">
-        <v>5.345548308534219</v>
+        <v>6.748678433766161</v>
       </c>
       <c r="G62">
-        <v>-5.728122228175394</v>
+        <v>-2.797094318980717</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.029221345552868</v>
       </c>
       <c r="E63">
-        <v>-15.85355106272644</v>
+        <v>-11.59946182365484</v>
       </c>
       <c r="F63">
-        <v>5.44616015654344</v>
+        <v>6.564938260151203</v>
       </c>
       <c r="G63">
-        <v>-6.040399367803767</v>
+        <v>-2.63146441510544</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.277597793919997</v>
       </c>
       <c r="E64">
-        <v>-15.69490956128973</v>
+        <v>-11.74373447706521</v>
       </c>
       <c r="F64">
-        <v>5.465553894177782</v>
+        <v>6.434024732547575</v>
       </c>
       <c r="G64">
-        <v>-6.061907982172412</v>
+        <v>-3.439571891787076</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.490813365189842</v>
       </c>
       <c r="E65">
-        <v>-16.01266805393395</v>
+        <v>-11.81319673986886</v>
       </c>
       <c r="F65">
-        <v>5.153501266603986</v>
+        <v>6.297902430715142</v>
       </c>
       <c r="G65">
-        <v>-6.72006098810722</v>
+        <v>-2.822714630909136</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.662798639742677</v>
       </c>
       <c r="E66">
-        <v>-14.52916713986519</v>
+        <v>-12.78873872449724</v>
       </c>
       <c r="F66">
-        <v>5.281149369905779</v>
+        <v>6.450895263072989</v>
       </c>
       <c r="G66">
-        <v>-6.842809395612317</v>
+        <v>-3.334193916726535</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.792858552646829</v>
       </c>
       <c r="E67">
-        <v>-14.1239909849769</v>
+        <v>-11.62162870392238</v>
       </c>
       <c r="F67">
-        <v>5.120313554978227</v>
+        <v>6.032322871173204</v>
       </c>
       <c r="G67">
-        <v>-6.491087105883529</v>
+        <v>-3.060352210809101</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.873813729158964</v>
       </c>
       <c r="E68">
-        <v>-14.8665792097027</v>
+        <v>-11.66485751679961</v>
       </c>
       <c r="F68">
-        <v>5.254948108955231</v>
+        <v>6.342208489621277</v>
       </c>
       <c r="G68">
-        <v>-6.530260791249725</v>
+        <v>-4.143244898886864</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.912901022658426</v>
       </c>
       <c r="E69">
-        <v>-14.13310680315434</v>
+        <v>-10.33464997636449</v>
       </c>
       <c r="F69">
-        <v>4.850587188217874</v>
+        <v>5.96258427626632</v>
       </c>
       <c r="G69">
-        <v>-6.341629216967592</v>
+        <v>-3.957821243232284</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.904035726358483</v>
       </c>
       <c r="E70">
-        <v>-12.91638734982546</v>
+        <v>-11.36359625496533</v>
       </c>
       <c r="F70">
-        <v>5.105045087009827</v>
+        <v>5.520582340745753</v>
       </c>
       <c r="G70">
-        <v>-6.677239081556747</v>
+        <v>-3.077510768339144</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.858275539177972</v>
       </c>
       <c r="E71">
-        <v>-14.28659037269631</v>
+        <v>-11.47371062893584</v>
       </c>
       <c r="F71">
-        <v>4.959779265785294</v>
+        <v>5.252583948387641</v>
       </c>
       <c r="G71">
-        <v>-6.583467879156891</v>
+        <v>-3.099913230003392</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.769495302300014</v>
       </c>
       <c r="E72">
-        <v>-13.79651438711222</v>
+        <v>-9.816298199076506</v>
       </c>
       <c r="F72">
-        <v>4.624838846872148</v>
+        <v>5.255340755104157</v>
       </c>
       <c r="G72">
-        <v>-6.489501354570217</v>
+        <v>-3.427259972926527</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.645695666061451</v>
       </c>
       <c r="E73">
-        <v>-13.4968788474467</v>
+        <v>-10.44912527080439</v>
       </c>
       <c r="F73">
-        <v>4.744668818626319</v>
+        <v>5.563635908138855</v>
       </c>
       <c r="G73">
-        <v>-6.742758088324464</v>
+        <v>-3.201507251512546</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.48301320999834</v>
       </c>
       <c r="E74">
-        <v>-13.77435656379269</v>
+        <v>-10.49188312238481</v>
       </c>
       <c r="F74">
-        <v>4.581806817031519</v>
+        <v>5.250213160880829</v>
       </c>
       <c r="G74">
-        <v>-6.460732713833951</v>
+        <v>-2.841121264107485</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.283819500908747</v>
       </c>
       <c r="E75">
-        <v>-14.72930304863418</v>
+        <v>-10.68839172347366</v>
       </c>
       <c r="F75">
-        <v>4.58312392120197</v>
+        <v>5.698784049905595</v>
       </c>
       <c r="G75">
-        <v>-6.60972381582885</v>
+        <v>-2.688250202740559</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.049400602775851</v>
       </c>
       <c r="E76">
-        <v>-14.03891907226881</v>
+        <v>-10.93743062305149</v>
       </c>
       <c r="F76">
-        <v>4.685992242016418</v>
+        <v>5.194987562870991</v>
       </c>
       <c r="G76">
-        <v>-6.743565861436045</v>
+        <v>-2.468006229103926</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.779915580669792</v>
       </c>
       <c r="E77">
-        <v>-14.48620550695442</v>
+        <v>-10.91686229410865</v>
       </c>
       <c r="F77">
-        <v>4.485466031351131</v>
+        <v>5.380916283164146</v>
       </c>
       <c r="G77">
-        <v>-6.533253524417225</v>
+        <v>-2.716585162011181</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.484082637699929</v>
       </c>
       <c r="E78">
-        <v>-14.5018377992289</v>
+        <v>-11.48826514439649</v>
       </c>
       <c r="F78">
-        <v>4.281614753931006</v>
+        <v>4.793562376209157</v>
       </c>
       <c r="G78">
-        <v>-6.33650118192726</v>
+        <v>-2.28797214158728</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.159974642903993</v>
       </c>
       <c r="E79">
-        <v>-15.41678427316064</v>
+        <v>-12.3210696283031</v>
       </c>
       <c r="F79">
-        <v>4.317252776334247</v>
+        <v>5.097598064058659</v>
       </c>
       <c r="G79">
-        <v>-6.066844005571465</v>
+        <v>-1.950617619498928</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.819273864028753</v>
       </c>
       <c r="E80">
-        <v>-14.91224434159605</v>
+        <v>-12.76919383068014</v>
       </c>
       <c r="F80">
-        <v>4.036111506763317</v>
+        <v>4.969833989320475</v>
       </c>
       <c r="G80">
-        <v>-5.738633210262581</v>
+        <v>-1.423777402379311</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.456335904565851</v>
       </c>
       <c r="E81">
-        <v>-16.37909858521262</v>
+        <v>-12.57000437297875</v>
       </c>
       <c r="F81">
-        <v>4.263644151494674</v>
+        <v>4.748277187032913</v>
       </c>
       <c r="G81">
-        <v>-5.479910765822998</v>
+        <v>-0.7797968418981227</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.080060924629035</v>
       </c>
       <c r="E82">
-        <v>-16.56967035687741</v>
+        <v>-12.82801870803978</v>
       </c>
       <c r="F82">
-        <v>3.933610981075712</v>
+        <v>4.730899695656985</v>
       </c>
       <c r="G82">
-        <v>-5.628723098358777</v>
+        <v>-1.050907347745658</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.6856668119552</v>
       </c>
       <c r="E83">
-        <v>-17.59177411125265</v>
+        <v>-12.89420688413589</v>
       </c>
       <c r="F83">
-        <v>4.105788802482394</v>
+        <v>4.506652356045131</v>
       </c>
       <c r="G83">
-        <v>-5.621572319993951</v>
+        <v>-0.9204453691340592</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.279524123838832</v>
       </c>
       <c r="E84">
-        <v>-18.31204148759465</v>
+        <v>-15.00617394946315</v>
       </c>
       <c r="F84">
-        <v>3.911902784917948</v>
+        <v>4.572119888623181</v>
       </c>
       <c r="G84">
-        <v>-4.945419877962125</v>
+        <v>-1.329714871971999</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.862408593021795</v>
       </c>
       <c r="E85">
-        <v>-18.09820694495246</v>
+        <v>-15.6805407132634</v>
       </c>
       <c r="F85">
-        <v>3.768858645067724</v>
+        <v>4.712735255248398</v>
       </c>
       <c r="G85">
-        <v>-4.402897606622981</v>
+        <v>-0.4725053838518926</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.438925955538434</v>
       </c>
       <c r="E86">
-        <v>-19.08539616472856</v>
+        <v>-16.65415356796451</v>
       </c>
       <c r="F86">
-        <v>3.858459833558935</v>
+        <v>4.616028331175972</v>
       </c>
       <c r="G86">
-        <v>-4.48207923483127</v>
+        <v>0.05648668786825035</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.016307906476544</v>
       </c>
       <c r="E87">
-        <v>-21.16525182086743</v>
+        <v>-17.56374285714518</v>
       </c>
       <c r="F87">
-        <v>3.752440403144237</v>
+        <v>4.316465827301587</v>
       </c>
       <c r="G87">
-        <v>-4.094533531822028</v>
+        <v>0.3871737712405099</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.599277958853023</v>
       </c>
       <c r="E88">
-        <v>-22.08182401696793</v>
+        <v>-18.8422397528867</v>
       </c>
       <c r="F88">
-        <v>3.654532346337752</v>
+        <v>4.42971856187753</v>
       </c>
       <c r="G88">
-        <v>-3.807363569563487</v>
+        <v>0.1463415148951489</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.201289819590047</v>
       </c>
       <c r="E89">
-        <v>-23.70462984846065</v>
+        <v>-20.39735395491276</v>
       </c>
       <c r="F89">
-        <v>3.542205726518139</v>
+        <v>3.777170483587414</v>
       </c>
       <c r="G89">
-        <v>-3.78019061177715</v>
+        <v>0.1054827618494639</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.827894930623773</v>
       </c>
       <c r="E90">
-        <v>-24.98698500405671</v>
+        <v>-21.36823613978725</v>
       </c>
       <c r="F90">
-        <v>2.994166136500014</v>
+        <v>4.225643625258649</v>
       </c>
       <c r="G90">
-        <v>-3.534372673849646</v>
+        <v>1.158679856439964</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.495396964972548</v>
       </c>
       <c r="E91">
-        <v>-26.2452124501399</v>
+        <v>-24.0982131098893</v>
       </c>
       <c r="F91">
-        <v>3.110765475383267</v>
+        <v>3.771332150132483</v>
       </c>
       <c r="G91">
-        <v>-3.57087474896565</v>
+        <v>1.114791954225846</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.205153038500808</v>
       </c>
       <c r="E92">
-        <v>-28.10357591408961</v>
+        <v>-24.6532364696914</v>
       </c>
       <c r="F92">
-        <v>3.187077993998769</v>
+        <v>3.521789783508743</v>
       </c>
       <c r="G92">
-        <v>-2.764545035238603</v>
+        <v>0.7766495222991473</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.968545126005215</v>
       </c>
       <c r="E93">
-        <v>-29.52097242883141</v>
+        <v>-26.80705116332355</v>
       </c>
       <c r="F93">
-        <v>2.463782369305158</v>
+        <v>3.308970600585911</v>
       </c>
       <c r="G93">
-        <v>-2.937444897118119</v>
+        <v>0.8745258011677</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.783467440054436</v>
       </c>
       <c r="E94">
-        <v>-31.75431844722326</v>
+        <v>-29.3658155881436</v>
       </c>
       <c r="F94">
-        <v>2.223683391073333</v>
+        <v>2.879806703073931</v>
       </c>
       <c r="G94">
-        <v>-3.206181741813997</v>
+        <v>1.442774321892521</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.653284932157049</v>
       </c>
       <c r="E95">
-        <v>-34.11497798386676</v>
+        <v>-31.22880941676615</v>
       </c>
       <c r="F95">
-        <v>1.800475455187482</v>
+        <v>2.987638601365954</v>
       </c>
       <c r="G95">
-        <v>-2.428514731365959</v>
+        <v>1.193827918430406</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.577092346279228</v>
       </c>
       <c r="E96">
-        <v>-35.90000960397326</v>
+        <v>-33.2397530196933</v>
       </c>
       <c r="F96">
-        <v>1.796605322681603</v>
+        <v>2.278349012718877</v>
       </c>
       <c r="G96">
-        <v>-2.413272979703155</v>
+        <v>0.6110229289694098</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.549128466212551</v>
       </c>
       <c r="E97">
-        <v>-38.38210243536944</v>
+        <v>-35.93352936857804</v>
       </c>
       <c r="F97">
-        <v>0.9714569556093761</v>
+        <v>1.781751038414602</v>
       </c>
       <c r="G97">
-        <v>-3.002490495873719</v>
+        <v>1.085099671284122</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.575032128958176</v>
       </c>
       <c r="E98">
-        <v>-40.98472286671678</v>
+        <v>-38.54355385492791</v>
       </c>
       <c r="F98">
-        <v>0.6851533003841997</v>
+        <v>1.866274334726652</v>
       </c>
       <c r="G98">
-        <v>-3.585513981340307</v>
+        <v>0.4106058125674714</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.638168017266852</v>
       </c>
       <c r="E99">
-        <v>-43.82128652953737</v>
+        <v>-40.59389065324778</v>
       </c>
       <c r="F99">
-        <v>0.2952647865411536</v>
+        <v>1.280447937262425</v>
       </c>
       <c r="G99">
-        <v>-3.124378161538606</v>
+        <v>0.9693629992312016</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.758075301731383</v>
       </c>
       <c r="E100">
-        <v>-46.18111961967447</v>
+        <v>-43.80012949897353</v>
       </c>
       <c r="F100">
-        <v>0.2269319311168196</v>
+        <v>1.050592550333618</v>
       </c>
       <c r="G100">
-        <v>-3.047437772660404</v>
+        <v>1.308535010820613</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.896904125874747</v>
       </c>
       <c r="E101">
-        <v>-47.42958141156012</v>
+        <v>-45.96800510439949</v>
       </c>
       <c r="F101">
-        <v>-0.5571550921660384</v>
+        <v>0.3330954974596043</v>
       </c>
       <c r="G101">
-        <v>-3.203685590477386</v>
+        <v>1.088410216823394</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.110921478688604</v>
       </c>
       <c r="E102">
-        <v>-51.29351317978987</v>
+        <v>-48.51778956526233</v>
       </c>
       <c r="F102">
-        <v>-0.8507641195165035</v>
+        <v>0.2432383434409279</v>
       </c>
       <c r="G102">
-        <v>-2.798163625189901</v>
+        <v>1.013876594552242</v>
       </c>
     </row>
   </sheetData>
